--- a/inst/extdata/utah_criteria_crosswalk.xlsx
+++ b/inst/extdata/utah_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{E9328460-6E84-4609-9736-FD6C54CAAA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15CC355D-BAFF-4D8A-8AAE-98D69CAB606A}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{E9328460-6E84-4609-9736-FD6C54CAAA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F172AD3A-05A2-4382-9C60-E31D4DAC5D36}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B782C4AB-D843-4051-84B7-77554F130E75}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B782C4AB-D843-4051-84B7-77554F130E75}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3754" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3757" uniqueCount="182">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -545,9 +545,6 @@
     <t>pHDirection</t>
   </si>
   <si>
-    <t>TemperatureExtreme</t>
-  </si>
-  <si>
     <t>pH_param_9</t>
   </si>
   <si>
@@ -569,10 +566,22 @@
     <t>MaxEqMagnitude</t>
   </si>
   <si>
-    <t>Min</t>
+    <t>AmmoniaEqType</t>
   </si>
   <si>
-    <t>Max</t>
+    <t>pH_param_10</t>
+  </si>
+  <si>
+    <t>pH_param_11</t>
+  </si>
+  <si>
+    <t>pH_param_12</t>
+  </si>
+  <si>
+    <t>Min Multiplier</t>
+  </si>
+  <si>
+    <t>Max Exponent</t>
   </si>
 </sst>
 </file>
@@ -985,20 +994,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0117CA-675B-45E3-8D8C-A5BB9123D964}">
-  <dimension ref="A1:AX325"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BA325"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="30" width="9.140625" style="5"/>
-    <col min="31" max="31" width="22.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="93.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="19.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="8.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="30" width="9.109375" style="5"/>
+    <col min="31" max="31" width="22.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="93.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="19.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="8.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1114,7 +1123,7 @@
         <v>34</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>35</v>
@@ -1129,28 +1138,37 @@
         <v>38</v>
       </c>
       <c r="AR1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="AS1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="AW1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="AX1" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -1217,7 +1235,7 @@
       <c r="AL2" s="3"/>
       <c r="AM2" s="3"/>
     </row>
-    <row r="3" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -1284,7 +1302,7 @@
       <c r="AL3" s="3"/>
       <c r="AM3" s="3"/>
     </row>
-    <row r="4" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>39</v>
@@ -1351,7 +1369,7 @@
       <c r="AL4" s="3"/>
       <c r="AM4" s="3"/>
     </row>
-    <row r="5" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>39</v>
@@ -1418,7 +1436,7 @@
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
     </row>
-    <row r="6" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -1485,7 +1503,7 @@
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
     </row>
-    <row r="7" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -1552,7 +1570,7 @@
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
     </row>
-    <row r="8" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -1621,7 +1639,7 @@
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
     </row>
-    <row r="9" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>39</v>
@@ -1690,7 +1708,7 @@
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
     </row>
-    <row r="10" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>39</v>
@@ -1759,7 +1777,7 @@
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
     </row>
-    <row r="11" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -1828,7 +1846,7 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>39</v>
@@ -1895,7 +1913,7 @@
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
     </row>
-    <row r="13" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -1962,7 +1980,7 @@
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
     </row>
-    <row r="14" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -2031,7 +2049,7 @@
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
     </row>
-    <row r="15" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -2100,7 +2118,7 @@
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
     </row>
-    <row r="16" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -2169,7 +2187,7 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -2238,7 +2256,7 @@
       <c r="AL17" s="3"/>
       <c r="AM17" s="3"/>
     </row>
-    <row r="18" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -2307,7 +2325,7 @@
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
     </row>
-    <row r="19" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -2376,7 +2394,7 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -2445,7 +2463,7 @@
       <c r="AL20" s="3"/>
       <c r="AM20" s="3"/>
     </row>
-    <row r="21" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -2514,7 +2532,7 @@
       <c r="AL21" s="3"/>
       <c r="AM21" s="3"/>
     </row>
-    <row r="22" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -2583,7 +2601,7 @@
       <c r="AL22" s="3"/>
       <c r="AM22" s="3"/>
     </row>
-    <row r="23" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>39</v>
@@ -2652,7 +2670,7 @@
       <c r="AL23" s="3"/>
       <c r="AM23" s="3"/>
     </row>
-    <row r="24" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -2721,7 +2739,7 @@
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
     </row>
-    <row r="25" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -2790,7 +2808,7 @@
       <c r="AL25" s="3"/>
       <c r="AM25" s="3"/>
     </row>
-    <row r="26" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -2859,7 +2877,7 @@
       <c r="AL26" s="3"/>
       <c r="AM26" s="3"/>
     </row>
-    <row r="27" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -2928,7 +2946,7 @@
       <c r="AL27" s="3"/>
       <c r="AM27" s="3"/>
     </row>
-    <row r="28" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>39</v>
@@ -2997,7 +3015,7 @@
       <c r="AL28" s="3"/>
       <c r="AM28" s="3"/>
     </row>
-    <row r="29" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -3066,7 +3084,7 @@
       <c r="AL29" s="3"/>
       <c r="AM29" s="3"/>
     </row>
-    <row r="30" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>39</v>
@@ -3135,7 +3153,7 @@
       <c r="AL30" s="3"/>
       <c r="AM30" s="3"/>
     </row>
-    <row r="31" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>39</v>
@@ -3204,7 +3222,7 @@
       <c r="AL31" s="3"/>
       <c r="AM31" s="3"/>
     </row>
-    <row r="32" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>39</v>
@@ -3273,7 +3291,7 @@
       <c r="AL32" s="3"/>
       <c r="AM32" s="3"/>
     </row>
-    <row r="33" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>39</v>
@@ -3342,7 +3360,7 @@
       <c r="AL33" s="3"/>
       <c r="AM33" s="3"/>
     </row>
-    <row r="34" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>39</v>
@@ -3409,7 +3427,7 @@
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
     </row>
-    <row r="35" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>39</v>
@@ -3476,7 +3494,7 @@
       <c r="AL35" s="3"/>
       <c r="AM35" s="3"/>
     </row>
-    <row r="36" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>39</v>
@@ -3543,7 +3561,7 @@
       <c r="AL36" s="3"/>
       <c r="AM36" s="3"/>
     </row>
-    <row r="37" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>39</v>
@@ -3610,7 +3628,7 @@
       <c r="AL37" s="3"/>
       <c r="AM37" s="3"/>
     </row>
-    <row r="38" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>39</v>
@@ -3679,7 +3697,7 @@
       <c r="AL38" s="3"/>
       <c r="AM38" s="3"/>
     </row>
-    <row r="39" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>39</v>
@@ -3748,7 +3766,7 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>39</v>
@@ -3817,7 +3835,7 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>39</v>
@@ -3886,7 +3904,7 @@
       <c r="AL41" s="3"/>
       <c r="AM41" s="3"/>
     </row>
-    <row r="42" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>39</v>
@@ -3953,7 +3971,7 @@
       <c r="AL42" s="3"/>
       <c r="AM42" s="3"/>
     </row>
-    <row r="43" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>39</v>
@@ -4020,7 +4038,7 @@
       <c r="AL43" s="3"/>
       <c r="AM43" s="3"/>
     </row>
-    <row r="44" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>39</v>
@@ -4087,7 +4105,7 @@
       <c r="AL44" s="3"/>
       <c r="AM44" s="3"/>
     </row>
-    <row r="45" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>39</v>
@@ -4154,7 +4172,7 @@
       <c r="AL45" s="3"/>
       <c r="AM45" s="3"/>
     </row>
-    <row r="46" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>39</v>
@@ -4221,7 +4239,7 @@
       <c r="AL46" s="3"/>
       <c r="AM46" s="3"/>
     </row>
-    <row r="47" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>39</v>
@@ -4288,7 +4306,7 @@
       <c r="AL47" s="3"/>
       <c r="AM47" s="3"/>
     </row>
-    <row r="48" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>39</v>
@@ -4357,7 +4375,7 @@
       <c r="AL48" s="3"/>
       <c r="AM48" s="3"/>
     </row>
-    <row r="49" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>39</v>
@@ -4426,7 +4444,7 @@
       <c r="AL49" s="3"/>
       <c r="AM49" s="3"/>
     </row>
-    <row r="50" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
         <v>39</v>
@@ -4495,7 +4513,7 @@
       <c r="AL50" s="3"/>
       <c r="AM50" s="3"/>
     </row>
-    <row r="51" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>39</v>
@@ -4564,7 +4582,7 @@
       <c r="AL51" s="3"/>
       <c r="AM51" s="3"/>
     </row>
-    <row r="52" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>39</v>
@@ -4631,7 +4649,7 @@
       <c r="AL52" s="3"/>
       <c r="AM52" s="3"/>
     </row>
-    <row r="53" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>39</v>
@@ -4698,7 +4716,7 @@
       <c r="AL53" s="3"/>
       <c r="AM53" s="3"/>
     </row>
-    <row r="54" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>39</v>
@@ -4765,7 +4783,7 @@
       <c r="AL54" s="3"/>
       <c r="AM54" s="3"/>
     </row>
-    <row r="55" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>39</v>
@@ -4832,7 +4850,7 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>39</v>
@@ -4905,7 +4923,7 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
         <v>39</v>
@@ -4978,7 +4996,7 @@
       <c r="AL57" s="3"/>
       <c r="AM57" s="3"/>
     </row>
-    <row r="58" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
         <v>39</v>
@@ -5051,7 +5069,7 @@
       <c r="AL58" s="3"/>
       <c r="AM58" s="3"/>
     </row>
-    <row r="59" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
         <v>39</v>
@@ -5124,7 +5142,7 @@
       <c r="AL59" s="3"/>
       <c r="AM59" s="3"/>
     </row>
-    <row r="60" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
         <v>39</v>
@@ -5193,7 +5211,7 @@
       <c r="AL60" s="3"/>
       <c r="AM60" s="3"/>
     </row>
-    <row r="61" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
         <v>39</v>
@@ -5262,7 +5280,7 @@
       <c r="AL61" s="3"/>
       <c r="AM61" s="3"/>
     </row>
-    <row r="62" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
         <v>39</v>
@@ -5331,7 +5349,7 @@
       <c r="AL62" s="3"/>
       <c r="AM62" s="3"/>
     </row>
-    <row r="63" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
         <v>39</v>
@@ -5400,7 +5418,7 @@
       <c r="AL63" s="3"/>
       <c r="AM63" s="3"/>
     </row>
-    <row r="64" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
         <v>39</v>
@@ -5469,7 +5487,7 @@
       <c r="AL64" s="3"/>
       <c r="AM64" s="3"/>
     </row>
-    <row r="65" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
         <v>39</v>
@@ -5538,7 +5556,7 @@
       <c r="AL65" s="3"/>
       <c r="AM65" s="3"/>
     </row>
-    <row r="66" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
         <v>39</v>
@@ -5607,7 +5625,7 @@
       <c r="AL66" s="3"/>
       <c r="AM66" s="3"/>
     </row>
-    <row r="67" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
         <v>39</v>
@@ -5676,7 +5694,7 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
         <v>39</v>
@@ -5745,7 +5763,7 @@
       <c r="AL68" s="3"/>
       <c r="AM68" s="3"/>
     </row>
-    <row r="69" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
         <v>39</v>
@@ -5814,7 +5832,7 @@
       <c r="AL69" s="3"/>
       <c r="AM69" s="3"/>
     </row>
-    <row r="70" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
         <v>39</v>
@@ -5883,7 +5901,7 @@
       <c r="AL70" s="3"/>
       <c r="AM70" s="3"/>
     </row>
-    <row r="71" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
         <v>39</v>
@@ -5952,7 +5970,7 @@
       <c r="AL71" s="3"/>
       <c r="AM71" s="3"/>
     </row>
-    <row r="72" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3" t="s">
         <v>39</v>
@@ -6021,7 +6039,7 @@
       <c r="AL72" s="3"/>
       <c r="AM72" s="3"/>
     </row>
-    <row r="73" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="3"/>
       <c r="B73" s="3" t="s">
         <v>39</v>
@@ -6090,7 +6108,7 @@
       <c r="AL73" s="3"/>
       <c r="AM73" s="3"/>
     </row>
-    <row r="74" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
       <c r="B74" s="3" t="s">
         <v>39</v>
@@ -6159,7 +6177,7 @@
       <c r="AL74" s="3"/>
       <c r="AM74" s="3"/>
     </row>
-    <row r="75" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3" t="s">
         <v>39</v>
@@ -6228,7 +6246,7 @@
       <c r="AL75" s="3"/>
       <c r="AM75" s="3"/>
     </row>
-    <row r="76" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
       <c r="B76" s="3" t="s">
         <v>39</v>
@@ -6297,7 +6315,7 @@
       <c r="AL76" s="3"/>
       <c r="AM76" s="3"/>
     </row>
-    <row r="77" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
       <c r="B77" s="3" t="s">
         <v>39</v>
@@ -6366,7 +6384,7 @@
       <c r="AL77" s="3"/>
       <c r="AM77" s="3"/>
     </row>
-    <row r="78" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
         <v>39</v>
@@ -6435,7 +6453,7 @@
       <c r="AL78" s="3"/>
       <c r="AM78" s="3"/>
     </row>
-    <row r="79" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
       <c r="B79" s="3" t="s">
         <v>39</v>
@@ -6504,7 +6522,7 @@
       <c r="AL79" s="3"/>
       <c r="AM79" s="3"/>
     </row>
-    <row r="80" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
       <c r="B80" s="3" t="s">
         <v>39</v>
@@ -6573,7 +6591,7 @@
       <c r="AL80" s="3"/>
       <c r="AM80" s="3"/>
     </row>
-    <row r="81" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
       <c r="B81" s="3" t="s">
         <v>39</v>
@@ -6642,7 +6660,7 @@
       <c r="AL81" s="3"/>
       <c r="AM81" s="3"/>
     </row>
-    <row r="82" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="B82" s="3" t="s">
         <v>39</v>
@@ -6711,7 +6729,7 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3" t="s">
         <v>39</v>
@@ -6780,7 +6798,7 @@
       <c r="AL83" s="3"/>
       <c r="AM83" s="3"/>
     </row>
-    <row r="84" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
       <c r="B84" s="3" t="s">
         <v>39</v>
@@ -6849,7 +6867,7 @@
       <c r="AL84" s="3"/>
       <c r="AM84" s="3"/>
     </row>
-    <row r="85" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3"/>
       <c r="B85" s="3" t="s">
         <v>39</v>
@@ -6918,7 +6936,7 @@
       <c r="AL85" s="3"/>
       <c r="AM85" s="3"/>
     </row>
-    <row r="86" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
       <c r="B86" s="3" t="s">
         <v>39</v>
@@ -6987,7 +7005,7 @@
       <c r="AL86" s="3"/>
       <c r="AM86" s="3"/>
     </row>
-    <row r="87" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3" t="s">
         <v>39</v>
@@ -7056,7 +7074,7 @@
       <c r="AL87" s="3"/>
       <c r="AM87" s="3"/>
     </row>
-    <row r="88" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
       <c r="B88" s="3" t="s">
         <v>39</v>
@@ -7125,7 +7143,7 @@
       <c r="AL88" s="3"/>
       <c r="AM88" s="3"/>
     </row>
-    <row r="89" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="3"/>
       <c r="B89" s="3" t="s">
         <v>39</v>
@@ -7194,7 +7212,7 @@
       <c r="AL89" s="3"/>
       <c r="AM89" s="3"/>
     </row>
-    <row r="90" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
       <c r="B90" s="3" t="s">
         <v>39</v>
@@ -7263,7 +7281,7 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3" t="s">
         <v>39</v>
@@ -7332,7 +7350,7 @@
       <c r="AL91" s="3"/>
       <c r="AM91" s="3"/>
     </row>
-    <row r="92" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3" t="s">
         <v>39</v>
@@ -7401,7 +7419,7 @@
       <c r="AL92" s="3"/>
       <c r="AM92" s="3"/>
     </row>
-    <row r="93" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
       <c r="B93" s="3" t="s">
         <v>39</v>
@@ -7470,7 +7488,7 @@
       <c r="AL93" s="3"/>
       <c r="AM93" s="3"/>
     </row>
-    <row r="94" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3" t="s">
         <v>39</v>
@@ -7539,7 +7557,7 @@
       <c r="AL94" s="3"/>
       <c r="AM94" s="3"/>
     </row>
-    <row r="95" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3" t="s">
         <v>39</v>
@@ -7608,7 +7626,7 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3" t="s">
         <v>39</v>
@@ -7675,7 +7693,7 @@
       <c r="AL96" s="3"/>
       <c r="AM96" s="3"/>
     </row>
-    <row r="97" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3" t="s">
         <v>39</v>
@@ -7742,7 +7760,7 @@
       <c r="AL97" s="3"/>
       <c r="AM97" s="3"/>
     </row>
-    <row r="98" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3" t="s">
         <v>39</v>
@@ -7809,7 +7827,7 @@
       <c r="AL98" s="3"/>
       <c r="AM98" s="3"/>
     </row>
-    <row r="99" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3" t="s">
         <v>39</v>
@@ -7876,7 +7894,7 @@
       <c r="AL99" s="3"/>
       <c r="AM99" s="3"/>
     </row>
-    <row r="100" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3" t="s">
         <v>39</v>
@@ -7945,7 +7963,7 @@
       <c r="AL100" s="3"/>
       <c r="AM100" s="3"/>
     </row>
-    <row r="101" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3" t="s">
         <v>39</v>
@@ -8014,7 +8032,7 @@
       <c r="AL101" s="3"/>
       <c r="AM101" s="3"/>
     </row>
-    <row r="102" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="3" t="s">
         <v>39</v>
@@ -8083,7 +8101,7 @@
       <c r="AL102" s="3"/>
       <c r="AM102" s="3"/>
     </row>
-    <row r="103" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3" t="s">
         <v>39</v>
@@ -8152,7 +8170,7 @@
       <c r="AL103" s="3"/>
       <c r="AM103" s="3"/>
     </row>
-    <row r="104" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3" t="s">
         <v>39</v>
@@ -8221,7 +8239,7 @@
       <c r="AL104" s="3"/>
       <c r="AM104" s="3"/>
     </row>
-    <row r="105" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="3" t="s">
         <v>39</v>
@@ -8290,7 +8308,7 @@
       <c r="AL105" s="3"/>
       <c r="AM105" s="3"/>
     </row>
-    <row r="106" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
       <c r="B106" s="3" t="s">
         <v>39</v>
@@ -8359,7 +8377,7 @@
       <c r="AL106" s="3"/>
       <c r="AM106" s="3"/>
     </row>
-    <row r="107" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3" t="s">
         <v>39</v>
@@ -8428,7 +8446,7 @@
       <c r="AL107" s="3"/>
       <c r="AM107" s="3"/>
     </row>
-    <row r="108" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3" t="s">
         <v>39</v>
@@ -8497,7 +8515,7 @@
       <c r="AL108" s="3"/>
       <c r="AM108" s="3"/>
     </row>
-    <row r="109" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
       <c r="B109" s="3" t="s">
         <v>39</v>
@@ -8566,7 +8584,7 @@
       <c r="AL109" s="3"/>
       <c r="AM109" s="3"/>
     </row>
-    <row r="110" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
       <c r="B110" s="3" t="s">
         <v>39</v>
@@ -8644,7 +8662,7 @@
         <v>0.68479999999999996</v>
       </c>
     </row>
-    <row r="111" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3" t="s">
         <v>39</v>
@@ -8722,7 +8740,7 @@
         <v>0.68479999999999996</v>
       </c>
     </row>
-    <row r="112" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="3" t="s">
         <v>39</v>
@@ -8800,7 +8818,7 @@
         <v>0.68479999999999996</v>
       </c>
     </row>
-    <row r="113" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
       <c r="B113" s="3" t="s">
         <v>39</v>
@@ -8878,7 +8896,7 @@
         <v>0.68479999999999996</v>
       </c>
     </row>
-    <row r="114" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>
       <c r="B114" s="3" t="s">
         <v>39</v>
@@ -8956,7 +8974,7 @@
         <v>3.7256</v>
       </c>
     </row>
-    <row r="115" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3" t="s">
         <v>39</v>
@@ -9034,7 +9052,7 @@
         <v>3.7256</v>
       </c>
     </row>
-    <row r="116" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
       <c r="B116" s="3" t="s">
         <v>39</v>
@@ -9112,7 +9130,7 @@
         <v>3.7256</v>
       </c>
     </row>
-    <row r="117" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A117" s="3"/>
       <c r="B117" s="3" t="s">
         <v>39</v>
@@ -9190,7 +9208,7 @@
         <v>3.7256</v>
       </c>
     </row>
-    <row r="118" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="3"/>
       <c r="B118" s="3" t="s">
         <v>39</v>
@@ -9259,7 +9277,7 @@
       <c r="AL118" s="3"/>
       <c r="AM118" s="3"/>
     </row>
-    <row r="119" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
       <c r="B119" s="3" t="s">
         <v>39</v>
@@ -9328,7 +9346,7 @@
       <c r="AL119" s="3"/>
       <c r="AM119" s="3"/>
     </row>
-    <row r="120" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="3" t="s">
         <v>39</v>
@@ -9406,7 +9424,7 @@
         <v>-1.702</v>
       </c>
     </row>
-    <row r="121" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="3" t="s">
         <v>39</v>
@@ -9484,7 +9502,7 @@
         <v>-1.702</v>
       </c>
     </row>
-    <row r="122" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="3" t="s">
         <v>39</v>
@@ -9562,7 +9580,7 @@
         <v>-1.702</v>
       </c>
     </row>
-    <row r="123" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="3" t="s">
         <v>39</v>
@@ -9640,7 +9658,7 @@
         <v>-1.702</v>
       </c>
     </row>
-    <row r="124" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="3" t="s">
         <v>39</v>
@@ -9718,7 +9736,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="125" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="3" t="s">
         <v>39</v>
@@ -9796,7 +9814,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="126" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="3" t="s">
         <v>39</v>
@@ -9874,7 +9892,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="127" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="3" t="s">
         <v>39</v>
@@ -9952,7 +9970,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="128" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="3" t="s">
         <v>39</v>
@@ -10021,7 +10039,7 @@
       <c r="AL128" s="3"/>
       <c r="AM128" s="3"/>
     </row>
-    <row r="129" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
       <c r="B129" s="3" t="s">
         <v>39</v>
@@ -10090,7 +10108,7 @@
       <c r="AL129" s="3"/>
       <c r="AM129" s="3"/>
     </row>
-    <row r="130" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
       <c r="B130" s="3" t="s">
         <v>39</v>
@@ -10159,7 +10177,7 @@
       <c r="AL130" s="3"/>
       <c r="AM130" s="3"/>
     </row>
-    <row r="131" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="3" t="s">
         <v>39</v>
@@ -10228,7 +10246,7 @@
       <c r="AL131" s="3"/>
       <c r="AM131" s="3"/>
     </row>
-    <row r="132" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="3" t="s">
         <v>39</v>
@@ -10297,7 +10315,7 @@
       <c r="AL132" s="3"/>
       <c r="AM132" s="3"/>
     </row>
-    <row r="133" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
       <c r="B133" s="3" t="s">
         <v>39</v>
@@ -10366,7 +10384,7 @@
       <c r="AL133" s="3"/>
       <c r="AM133" s="3"/>
     </row>
-    <row r="134" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="3" t="s">
         <v>39</v>
@@ -10435,7 +10453,7 @@
       <c r="AL134" s="3"/>
       <c r="AM134" s="3"/>
     </row>
-    <row r="135" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="3" t="s">
         <v>39</v>
@@ -10504,7 +10522,7 @@
       <c r="AL135" s="3"/>
       <c r="AM135" s="3"/>
     </row>
-    <row r="136" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
       <c r="B136" s="3" t="s">
         <v>39</v>
@@ -10573,7 +10591,7 @@
       <c r="AL136" s="3"/>
       <c r="AM136" s="3"/>
     </row>
-    <row r="137" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="3"/>
       <c r="B137" s="3" t="s">
         <v>39</v>
@@ -10642,7 +10660,7 @@
       <c r="AL137" s="3"/>
       <c r="AM137" s="3"/>
     </row>
-    <row r="138" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="3"/>
       <c r="B138" s="3" t="s">
         <v>39</v>
@@ -10711,7 +10729,7 @@
       <c r="AL138" s="3"/>
       <c r="AM138" s="3"/>
     </row>
-    <row r="139" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="3" t="s">
         <v>39</v>
@@ -10780,7 +10798,7 @@
       <c r="AL139" s="3"/>
       <c r="AM139" s="3"/>
     </row>
-    <row r="140" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
       <c r="B140" s="3" t="s">
         <v>39</v>
@@ -10849,7 +10867,7 @@
       <c r="AL140" s="3"/>
       <c r="AM140" s="3"/>
     </row>
-    <row r="141" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="3"/>
       <c r="B141" s="3" t="s">
         <v>39</v>
@@ -10918,7 +10936,7 @@
       <c r="AL141" s="3"/>
       <c r="AM141" s="3"/>
     </row>
-    <row r="142" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="3"/>
       <c r="B142" s="3" t="s">
         <v>39</v>
@@ -10987,7 +11005,7 @@
       <c r="AL142" s="3"/>
       <c r="AM142" s="3"/>
     </row>
-    <row r="143" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="3" t="s">
         <v>39</v>
@@ -11056,7 +11074,7 @@
       <c r="AL143" s="3"/>
       <c r="AM143" s="3"/>
     </row>
-    <row r="144" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="3" t="s">
         <v>39</v>
@@ -11125,7 +11143,7 @@
       <c r="AL144" s="3"/>
       <c r="AM144" s="3"/>
     </row>
-    <row r="145" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
       <c r="B145" s="3" t="s">
         <v>39</v>
@@ -11194,7 +11212,7 @@
       <c r="AL145" s="3"/>
       <c r="AM145" s="3"/>
     </row>
-    <row r="146" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
       <c r="B146" s="3" t="s">
         <v>39</v>
@@ -11261,7 +11279,7 @@
       <c r="AL146" s="3"/>
       <c r="AM146" s="3"/>
     </row>
-    <row r="147" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
       <c r="B147" s="3" t="s">
         <v>39</v>
@@ -11330,7 +11348,7 @@
       <c r="AL147" s="3"/>
       <c r="AM147" s="3"/>
     </row>
-    <row r="148" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
       <c r="B148" s="3" t="s">
         <v>39</v>
@@ -11399,7 +11417,7 @@
       <c r="AL148" s="3"/>
       <c r="AM148" s="3"/>
     </row>
-    <row r="149" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
       <c r="B149" s="3" t="s">
         <v>39</v>
@@ -11468,7 +11486,7 @@
       <c r="AL149" s="3"/>
       <c r="AM149" s="3"/>
     </row>
-    <row r="150" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150" s="3"/>
       <c r="B150" s="3" t="s">
         <v>39</v>
@@ -11537,7 +11555,7 @@
       <c r="AL150" s="3"/>
       <c r="AM150" s="3"/>
     </row>
-    <row r="151" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
       <c r="B151" s="3" t="s">
         <v>39</v>
@@ -11606,7 +11624,7 @@
       <c r="AL151" s="3"/>
       <c r="AM151" s="3"/>
     </row>
-    <row r="152" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
       <c r="B152" s="3" t="s">
         <v>39</v>
@@ -11675,7 +11693,7 @@
       <c r="AL152" s="3"/>
       <c r="AM152" s="3"/>
     </row>
-    <row r="153" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="3"/>
       <c r="B153" s="3" t="s">
         <v>39</v>
@@ -11744,7 +11762,7 @@
       <c r="AL153" s="3"/>
       <c r="AM153" s="3"/>
     </row>
-    <row r="154" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="3"/>
       <c r="B154" s="3" t="s">
         <v>39</v>
@@ -11813,7 +11831,7 @@
       <c r="AL154" s="3"/>
       <c r="AM154" s="3"/>
     </row>
-    <row r="155" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155" s="3"/>
       <c r="B155" s="3" t="s">
         <v>39</v>
@@ -11882,7 +11900,7 @@
       <c r="AL155" s="3"/>
       <c r="AM155" s="3"/>
     </row>
-    <row r="156" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="3"/>
       <c r="B156" s="3" t="s">
         <v>39</v>
@@ -11951,7 +11969,7 @@
       <c r="AL156" s="3"/>
       <c r="AM156" s="3"/>
     </row>
-    <row r="157" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A157" s="3"/>
       <c r="B157" s="3" t="s">
         <v>39</v>
@@ -12020,7 +12038,7 @@
       <c r="AL157" s="3"/>
       <c r="AM157" s="3"/>
     </row>
-    <row r="158" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158" s="3"/>
       <c r="B158" s="3" t="s">
         <v>39</v>
@@ -12098,7 +12116,7 @@
         <v>5.8400000000000001E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A159" s="3"/>
       <c r="B159" s="3" t="s">
         <v>39</v>
@@ -12176,7 +12194,7 @@
         <v>5.8400000000000001E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A160" s="3"/>
       <c r="B160" s="3" t="s">
         <v>39</v>
@@ -12254,7 +12272,7 @@
         <v>5.8400000000000001E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A161" s="3"/>
       <c r="B161" s="3" t="s">
         <v>39</v>
@@ -12332,7 +12350,7 @@
         <v>5.8400000000000001E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A162" s="3"/>
       <c r="B162" s="3" t="s">
         <v>39</v>
@@ -12410,7 +12428,7 @@
         <v>2.2549999999999999</v>
       </c>
     </row>
-    <row r="163" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A163" s="3"/>
       <c r="B163" s="3" t="s">
         <v>39</v>
@@ -12488,7 +12506,7 @@
         <v>2.2549999999999999</v>
       </c>
     </row>
-    <row r="164" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A164" s="3"/>
       <c r="B164" s="3" t="s">
         <v>39</v>
@@ -12566,7 +12584,7 @@
         <v>2.2549999999999999</v>
       </c>
     </row>
-    <row r="165" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A165" s="3"/>
       <c r="B165" s="3" t="s">
         <v>39</v>
@@ -12644,7 +12662,7 @@
         <v>2.2549999999999999</v>
       </c>
     </row>
-    <row r="166" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A166" s="3"/>
       <c r="B166" s="3" t="s">
         <v>39</v>
@@ -12713,7 +12731,7 @@
       <c r="AL166" s="3"/>
       <c r="AM166" s="3"/>
     </row>
-    <row r="167" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167" s="3"/>
       <c r="B167" s="3" t="s">
         <v>39</v>
@@ -12783,7 +12801,7 @@
       <c r="AK167" s="3"/>
       <c r="AL167" s="3"/>
       <c r="AM167" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AN167" s="5">
         <v>5.7700000000000001E-2</v>
@@ -12813,7 +12831,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="168" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A168" s="3"/>
       <c r="B168" s="3" t="s">
         <v>39</v>
@@ -12883,7 +12901,7 @@
       <c r="AK168" s="3"/>
       <c r="AL168" s="3"/>
       <c r="AM168" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AN168" s="5">
         <v>5.7700000000000001E-2</v>
@@ -12913,7 +12931,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A169" s="3"/>
       <c r="B169" s="3" t="s">
         <v>39</v>
@@ -12983,7 +13001,7 @@
       <c r="AK169" s="3"/>
       <c r="AL169" s="3"/>
       <c r="AM169" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AN169" s="5">
         <v>5.7700000000000001E-2</v>
@@ -13013,7 +13031,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="170" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A170" s="3"/>
       <c r="B170" s="3" t="s">
         <v>39</v>
@@ -13083,7 +13101,7 @@
       <c r="AK170" s="3"/>
       <c r="AL170" s="3"/>
       <c r="AM170" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AN170" s="5">
         <v>5.7700000000000001E-2</v>
@@ -13113,7 +13131,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="171" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A171" s="3"/>
       <c r="B171" s="3" t="s">
         <v>39</v>
@@ -13196,7 +13214,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="172" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A172" s="3"/>
       <c r="B172" s="3" t="s">
         <v>39</v>
@@ -13279,7 +13297,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="173" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A173" s="3"/>
       <c r="B173" s="3" t="s">
         <v>39</v>
@@ -13362,7 +13380,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="174" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A174" s="3"/>
       <c r="B174" s="3" t="s">
         <v>39</v>
@@ -13445,7 +13463,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="175" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A175" s="3"/>
       <c r="B175" s="3" t="s">
         <v>39</v>
@@ -13515,7 +13533,7 @@
       <c r="AK175" s="3"/>
       <c r="AL175" s="3"/>
       <c r="AM175" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AN175" s="5">
         <v>5.7700000000000001E-2</v>
@@ -13545,7 +13563,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="176" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A176" s="3"/>
       <c r="B176" s="3" t="s">
         <v>39</v>
@@ -13615,7 +13633,7 @@
       <c r="AK176" s="3"/>
       <c r="AL176" s="3"/>
       <c r="AM176" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AN176" s="5">
         <v>5.7700000000000001E-2</v>
@@ -13645,7 +13663,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A177" s="3"/>
       <c r="B177" s="3" t="s">
         <v>39</v>
@@ -13715,7 +13733,7 @@
       <c r="AK177" s="3"/>
       <c r="AL177" s="3"/>
       <c r="AM177" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AN177" s="5">
         <v>5.7700000000000001E-2</v>
@@ -13745,7 +13763,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="178" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A178" s="3"/>
       <c r="B178" s="3" t="s">
         <v>39</v>
@@ -13815,7 +13833,7 @@
       <c r="AK178" s="3"/>
       <c r="AL178" s="3"/>
       <c r="AM178" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AN178" s="5">
         <v>5.7700000000000001E-2</v>
@@ -13845,7 +13863,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179" s="3"/>
       <c r="B179" s="3" t="s">
         <v>39</v>
@@ -13925,7 +13943,7 @@
         <v>-3.9089999999999998</v>
       </c>
     </row>
-    <row r="180" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A180" s="3"/>
       <c r="B180" s="3" t="s">
         <v>39</v>
@@ -14005,7 +14023,7 @@
         <v>-3.9089999999999998</v>
       </c>
     </row>
-    <row r="181" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A181" s="3"/>
       <c r="B181" s="3" t="s">
         <v>39</v>
@@ -14085,7 +14103,7 @@
         <v>-3.9089999999999998</v>
       </c>
     </row>
-    <row r="182" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A182" s="3"/>
       <c r="B182" s="3" t="s">
         <v>39</v>
@@ -14165,7 +14183,7 @@
         <v>-3.9089999999999998</v>
       </c>
     </row>
-    <row r="183" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A183" s="3"/>
       <c r="B183" s="3" t="s">
         <v>39</v>
@@ -14245,7 +14263,7 @@
         <v>-3.8660000000000001</v>
       </c>
     </row>
-    <row r="184" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A184" s="3"/>
       <c r="B184" s="3" t="s">
         <v>39</v>
@@ -14325,7 +14343,7 @@
         <v>-3.8660000000000001</v>
       </c>
     </row>
-    <row r="185" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A185" s="3"/>
       <c r="B185" s="3" t="s">
         <v>39</v>
@@ -14405,7 +14423,7 @@
         <v>-3.8660000000000001</v>
       </c>
     </row>
-    <row r="186" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A186" s="3"/>
       <c r="B186" s="3" t="s">
         <v>39</v>
@@ -14485,7 +14503,7 @@
         <v>-3.8660000000000001</v>
       </c>
     </row>
-    <row r="187" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A187" s="3"/>
       <c r="B187" s="3" t="s">
         <v>39</v>
@@ -14554,7 +14572,7 @@
       <c r="AL187" s="3"/>
       <c r="AM187" s="3"/>
     </row>
-    <row r="188" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A188" s="3"/>
       <c r="B188" s="3" t="s">
         <v>39</v>
@@ -14623,7 +14641,7 @@
       <c r="AL188" s="3"/>
       <c r="AM188" s="3"/>
     </row>
-    <row r="189" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A189" s="3"/>
       <c r="B189" s="3" t="s">
         <v>39</v>
@@ -14692,7 +14710,7 @@
       <c r="AL189" s="3"/>
       <c r="AM189" s="3"/>
     </row>
-    <row r="190" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A190" s="3"/>
       <c r="B190" s="3" t="s">
         <v>39</v>
@@ -14761,7 +14779,7 @@
       <c r="AL190" s="3"/>
       <c r="AM190" s="3"/>
     </row>
-    <row r="191" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A191" s="3"/>
       <c r="B191" s="3" t="s">
         <v>39</v>
@@ -14830,7 +14848,7 @@
       <c r="AL191" s="3"/>
       <c r="AM191" s="3"/>
     </row>
-    <row r="192" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A192" s="3"/>
       <c r="B192" s="3" t="s">
         <v>39</v>
@@ -14899,7 +14917,7 @@
       <c r="AL192" s="3"/>
       <c r="AM192" s="3"/>
     </row>
-    <row r="193" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A193" s="3"/>
       <c r="B193" s="3" t="s">
         <v>39</v>
@@ -14968,7 +14986,7 @@
       <c r="AL193" s="3"/>
       <c r="AM193" s="3"/>
     </row>
-    <row r="194" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A194" s="3"/>
       <c r="B194" s="3" t="s">
         <v>39</v>
@@ -15037,7 +15055,7 @@
       <c r="AL194" s="3"/>
       <c r="AM194" s="3"/>
     </row>
-    <row r="195" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A195" s="3"/>
       <c r="B195" s="3" t="s">
         <v>39</v>
@@ -15106,7 +15124,7 @@
       <c r="AL195" s="3"/>
       <c r="AM195" s="3"/>
     </row>
-    <row r="196" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A196" s="3"/>
       <c r="B196" s="3" t="s">
         <v>39</v>
@@ -15175,7 +15193,7 @@
       <c r="AL196" s="3"/>
       <c r="AM196" s="3"/>
     </row>
-    <row r="197" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A197" s="3"/>
       <c r="B197" s="3" t="s">
         <v>39</v>
@@ -15244,7 +15262,7 @@
       <c r="AL197" s="3"/>
       <c r="AM197" s="3"/>
     </row>
-    <row r="198" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A198" s="3"/>
       <c r="B198" s="3" t="s">
         <v>39</v>
@@ -15313,7 +15331,7 @@
       <c r="AL198" s="3"/>
       <c r="AM198" s="3"/>
     </row>
-    <row r="199" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A199" s="3"/>
       <c r="B199" s="3" t="s">
         <v>39</v>
@@ -15382,7 +15400,7 @@
       <c r="AL199" s="3"/>
       <c r="AM199" s="3"/>
     </row>
-    <row r="200" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A200" s="3"/>
       <c r="B200" s="3" t="s">
         <v>39</v>
@@ -15451,7 +15469,7 @@
       <c r="AL200" s="3"/>
       <c r="AM200" s="3"/>
     </row>
-    <row r="201" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A201" s="3"/>
       <c r="B201" s="3" t="s">
         <v>39</v>
@@ -15520,7 +15538,7 @@
       <c r="AL201" s="3"/>
       <c r="AM201" s="3"/>
     </row>
-    <row r="202" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A202" s="3"/>
       <c r="B202" s="3" t="s">
         <v>39</v>
@@ -15589,7 +15607,7 @@
       <c r="AL202" s="3"/>
       <c r="AM202" s="3"/>
     </row>
-    <row r="203" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A203" s="3"/>
       <c r="B203" s="3" t="s">
         <v>39</v>
@@ -15663,16 +15681,13 @@
         <v>0.14571200000000001</v>
       </c>
       <c r="AK203" s="3">
-        <v>1</v>
+        <v>1.2729999999999999</v>
       </c>
       <c r="AL203" s="3">
-        <v>1.2729999999999999</v>
-      </c>
-      <c r="AM203" s="3">
         <v>-4.7050000000000001</v>
       </c>
     </row>
-    <row r="204" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A204" s="3"/>
       <c r="B204" s="3" t="s">
         <v>39</v>
@@ -15746,16 +15761,13 @@
         <v>0.14571200000000001</v>
       </c>
       <c r="AK204" s="3">
-        <v>1</v>
+        <v>1.2729999999999999</v>
       </c>
       <c r="AL204" s="3">
-        <v>1.2729999999999999</v>
-      </c>
-      <c r="AM204" s="3">
         <v>-4.7050000000000001</v>
       </c>
     </row>
-    <row r="205" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A205" s="3"/>
       <c r="B205" s="3" t="s">
         <v>39</v>
@@ -15829,16 +15841,13 @@
         <v>0.14571200000000001</v>
       </c>
       <c r="AK205" s="3">
-        <v>1</v>
+        <v>1.2729999999999999</v>
       </c>
       <c r="AL205" s="3">
-        <v>1.2729999999999999</v>
-      </c>
-      <c r="AM205" s="3">
         <v>-4.7050000000000001</v>
       </c>
     </row>
-    <row r="206" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A206" s="3"/>
       <c r="B206" s="3" t="s">
         <v>39</v>
@@ -15912,16 +15921,13 @@
         <v>0.14571200000000001</v>
       </c>
       <c r="AK206" s="3">
-        <v>1</v>
+        <v>1.2729999999999999</v>
       </c>
       <c r="AL206" s="3">
-        <v>1.2729999999999999</v>
-      </c>
-      <c r="AM206" s="3">
         <v>-4.7050000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A207" s="3"/>
       <c r="B207" s="3" t="s">
         <v>39</v>
@@ -15995,16 +16001,13 @@
         <v>0.14571200000000001</v>
       </c>
       <c r="AK207" s="3">
-        <v>1</v>
+        <v>1.2729999999999999</v>
       </c>
       <c r="AL207" s="3">
-        <v>1.2729999999999999</v>
-      </c>
-      <c r="AM207" s="3">
         <v>-1.46</v>
       </c>
     </row>
-    <row r="208" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A208" s="3"/>
       <c r="B208" s="3" t="s">
         <v>39</v>
@@ -16078,16 +16081,13 @@
         <v>0.14571200000000001</v>
       </c>
       <c r="AK208" s="3">
-        <v>1</v>
+        <v>1.2729999999999999</v>
       </c>
       <c r="AL208" s="3">
-        <v>1.2729999999999999</v>
-      </c>
-      <c r="AM208" s="3">
         <v>-1.46</v>
       </c>
     </row>
-    <row r="209" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A209" s="3"/>
       <c r="B209" s="3" t="s">
         <v>39</v>
@@ -16161,16 +16161,13 @@
         <v>0.14571200000000001</v>
       </c>
       <c r="AK209" s="3">
-        <v>1</v>
+        <v>1.2729999999999999</v>
       </c>
       <c r="AL209" s="3">
-        <v>1.2729999999999999</v>
-      </c>
-      <c r="AM209" s="3">
         <v>-1.46</v>
       </c>
     </row>
-    <row r="210" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A210" s="3"/>
       <c r="B210" s="3" t="s">
         <v>39</v>
@@ -16244,16 +16241,13 @@
         <v>0.14571200000000001</v>
       </c>
       <c r="AK210" s="3">
-        <v>1</v>
+        <v>1.2729999999999999</v>
       </c>
       <c r="AL210" s="3">
-        <v>1.2729999999999999</v>
-      </c>
-      <c r="AM210" s="3">
         <v>-1.46</v>
       </c>
     </row>
-    <row r="211" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A211" s="3"/>
       <c r="B211" s="3" t="s">
         <v>39</v>
@@ -16322,7 +16316,7 @@
       <c r="AL211" s="3"/>
       <c r="AM211" s="3"/>
     </row>
-    <row r="212" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A212" s="3"/>
       <c r="B212" s="3" t="s">
         <v>39</v>
@@ -16391,7 +16385,7 @@
       <c r="AL212" s="3"/>
       <c r="AM212" s="3"/>
     </row>
-    <row r="213" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A213" s="3"/>
       <c r="B213" s="3" t="s">
         <v>39</v>
@@ -16458,7 +16452,7 @@
       <c r="AL213" s="3"/>
       <c r="AM213" s="3"/>
     </row>
-    <row r="214" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A214" s="3"/>
       <c r="B214" s="3" t="s">
         <v>39</v>
@@ -16527,7 +16521,7 @@
       <c r="AL214" s="3"/>
       <c r="AM214" s="3"/>
     </row>
-    <row r="215" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A215" s="3"/>
       <c r="B215" s="3" t="s">
         <v>39</v>
@@ -16596,7 +16590,7 @@
       <c r="AL215" s="3"/>
       <c r="AM215" s="3"/>
     </row>
-    <row r="216" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A216" s="3"/>
       <c r="B216" s="3" t="s">
         <v>39</v>
@@ -16665,7 +16659,7 @@
       <c r="AL216" s="3"/>
       <c r="AM216" s="3"/>
     </row>
-    <row r="217" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A217" s="3"/>
       <c r="B217" s="3" t="s">
         <v>39</v>
@@ -16734,7 +16728,7 @@
       <c r="AL217" s="3"/>
       <c r="AM217" s="3"/>
     </row>
-    <row r="218" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A218" s="3"/>
       <c r="B218" s="3" t="s">
         <v>39</v>
@@ -16803,7 +16797,7 @@
       <c r="AL218" s="3"/>
       <c r="AM218" s="3"/>
     </row>
-    <row r="219" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A219" s="3"/>
       <c r="B219" s="3" t="s">
         <v>39</v>
@@ -16872,7 +16866,7 @@
       <c r="AL219" s="3"/>
       <c r="AM219" s="3"/>
     </row>
-    <row r="220" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A220" s="3"/>
       <c r="B220" s="3" t="s">
         <v>39</v>
@@ -16940,18 +16934,17 @@
       <c r="AG220" s="3"/>
       <c r="AH220" s="3"/>
       <c r="AI220" s="3"/>
-      <c r="AJ220" s="3"/>
+      <c r="AJ220" s="3">
+        <v>0.85</v>
+      </c>
       <c r="AK220" s="3">
-        <v>0.85</v>
+        <v>1.72</v>
       </c>
       <c r="AL220" s="3">
-        <v>1.72</v>
-      </c>
-      <c r="AM220" s="3">
         <v>-6.59</v>
       </c>
     </row>
-    <row r="221" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A221" s="3"/>
       <c r="B221" s="3" t="s">
         <v>39</v>
@@ -17019,18 +17012,17 @@
       <c r="AG221" s="3"/>
       <c r="AH221" s="3"/>
       <c r="AI221" s="3"/>
-      <c r="AJ221" s="3"/>
+      <c r="AJ221" s="3">
+        <v>0.85</v>
+      </c>
       <c r="AK221" s="3">
-        <v>0.85</v>
+        <v>1.72</v>
       </c>
       <c r="AL221" s="3">
-        <v>1.72</v>
-      </c>
-      <c r="AM221" s="3">
         <v>-6.59</v>
       </c>
     </row>
-    <row r="222" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A222" s="3"/>
       <c r="B222" s="3" t="s">
         <v>39</v>
@@ -17098,18 +17090,17 @@
       <c r="AG222" s="3"/>
       <c r="AH222" s="3"/>
       <c r="AI222" s="3"/>
-      <c r="AJ222" s="3"/>
+      <c r="AJ222" s="3">
+        <v>0.85</v>
+      </c>
       <c r="AK222" s="3">
-        <v>0.85</v>
+        <v>1.72</v>
       </c>
       <c r="AL222" s="3">
-        <v>1.72</v>
-      </c>
-      <c r="AM222" s="3">
         <v>-6.59</v>
       </c>
     </row>
-    <row r="223" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A223" s="3"/>
       <c r="B223" s="3" t="s">
         <v>39</v>
@@ -17177,18 +17168,17 @@
       <c r="AG223" s="3"/>
       <c r="AH223" s="3"/>
       <c r="AI223" s="3"/>
-      <c r="AJ223" s="3"/>
+      <c r="AJ223" s="3">
+        <v>0.85</v>
+      </c>
       <c r="AK223" s="3">
-        <v>0.85</v>
+        <v>1.72</v>
       </c>
       <c r="AL223" s="3">
-        <v>1.72</v>
-      </c>
-      <c r="AM223" s="3">
         <v>-6.59</v>
       </c>
     </row>
-    <row r="224" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A224" s="3"/>
       <c r="B224" s="3" t="s">
         <v>39</v>
@@ -17256,18 +17246,17 @@
       <c r="AG224" s="3"/>
       <c r="AH224" s="3"/>
       <c r="AI224" s="3"/>
-      <c r="AJ224" s="3"/>
+      <c r="AJ224" s="3">
+        <v>0.98599999999999999</v>
+      </c>
       <c r="AK224" s="3">
-        <v>0.98599999999999999</v>
+        <v>0.84730000000000005</v>
       </c>
       <c r="AL224" s="3">
-        <v>0.84730000000000005</v>
-      </c>
-      <c r="AM224" s="3">
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="225" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A225" s="3"/>
       <c r="B225" s="3" t="s">
         <v>39</v>
@@ -17335,18 +17324,17 @@
       <c r="AG225" s="3"/>
       <c r="AH225" s="3"/>
       <c r="AI225" s="3"/>
-      <c r="AJ225" s="3"/>
+      <c r="AJ225" s="3">
+        <v>0.98599999999999999</v>
+      </c>
       <c r="AK225" s="3">
-        <v>0.98599999999999999</v>
+        <v>0.84730000000000005</v>
       </c>
       <c r="AL225" s="3">
-        <v>0.84730000000000005</v>
-      </c>
-      <c r="AM225" s="3">
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="226" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A226" s="3"/>
       <c r="B226" s="3" t="s">
         <v>39</v>
@@ -17414,18 +17402,17 @@
       <c r="AG226" s="3"/>
       <c r="AH226" s="3"/>
       <c r="AI226" s="3"/>
-      <c r="AJ226" s="3"/>
+      <c r="AJ226" s="3">
+        <v>0.98599999999999999</v>
+      </c>
       <c r="AK226" s="3">
-        <v>0.98599999999999999</v>
+        <v>0.84730000000000005</v>
       </c>
       <c r="AL226" s="3">
-        <v>0.84730000000000005</v>
-      </c>
-      <c r="AM226" s="3">
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="227" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A227" s="3"/>
       <c r="B227" s="3" t="s">
         <v>39</v>
@@ -17493,18 +17480,17 @@
       <c r="AG227" s="3"/>
       <c r="AH227" s="3"/>
       <c r="AI227" s="3"/>
-      <c r="AJ227" s="3"/>
+      <c r="AJ227" s="3">
+        <v>0.98599999999999999</v>
+      </c>
       <c r="AK227" s="3">
-        <v>0.98599999999999999</v>
+        <v>0.84730000000000005</v>
       </c>
       <c r="AL227" s="3">
-        <v>0.84730000000000005</v>
-      </c>
-      <c r="AM227" s="3">
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="228" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A228" s="3"/>
       <c r="B228" s="3" t="s">
         <v>39</v>
@@ -17572,18 +17558,17 @@
       <c r="AG228" s="3"/>
       <c r="AH228" s="3"/>
       <c r="AI228" s="3"/>
-      <c r="AJ228" s="3"/>
+      <c r="AJ228" s="3">
+        <v>0.97799999999999998</v>
+      </c>
       <c r="AK228" s="3">
-        <v>0.97799999999999998</v>
+        <v>0.84730000000000005</v>
       </c>
       <c r="AL228" s="3">
-        <v>0.84730000000000005</v>
-      </c>
-      <c r="AM228" s="3">
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="229" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A229" s="3"/>
       <c r="B229" s="3" t="s">
         <v>39</v>
@@ -17651,18 +17636,17 @@
       <c r="AG229" s="3"/>
       <c r="AH229" s="3"/>
       <c r="AI229" s="3"/>
-      <c r="AJ229" s="3"/>
+      <c r="AJ229" s="3">
+        <v>0.97799999999999998</v>
+      </c>
       <c r="AK229" s="3">
-        <v>0.97799999999999998</v>
+        <v>0.84730000000000005</v>
       </c>
       <c r="AL229" s="3">
-        <v>0.84730000000000005</v>
-      </c>
-      <c r="AM229" s="3">
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="230" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A230" s="3"/>
       <c r="B230" s="3" t="s">
         <v>39</v>
@@ -17730,18 +17714,17 @@
       <c r="AG230" s="3"/>
       <c r="AH230" s="3"/>
       <c r="AI230" s="3"/>
-      <c r="AJ230" s="3"/>
+      <c r="AJ230" s="3">
+        <v>0.97799999999999998</v>
+      </c>
       <c r="AK230" s="3">
-        <v>0.97799999999999998</v>
+        <v>0.84730000000000005</v>
       </c>
       <c r="AL230" s="3">
-        <v>0.84730000000000005</v>
-      </c>
-      <c r="AM230" s="3">
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="231" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A231" s="3"/>
       <c r="B231" s="3" t="s">
         <v>39</v>
@@ -17809,18 +17792,17 @@
       <c r="AG231" s="3"/>
       <c r="AH231" s="3"/>
       <c r="AI231" s="3"/>
-      <c r="AJ231" s="3"/>
+      <c r="AJ231" s="3">
+        <v>0.97799999999999998</v>
+      </c>
       <c r="AK231" s="3">
-        <v>0.97799999999999998</v>
+        <v>0.84730000000000005</v>
       </c>
       <c r="AL231" s="3">
-        <v>0.84730000000000005</v>
-      </c>
-      <c r="AM231" s="3">
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="232" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A232" s="3"/>
       <c r="B232" s="3" t="s">
         <v>39</v>
@@ -17889,7 +17871,7 @@
       <c r="AL232" s="3"/>
       <c r="AM232" s="3"/>
     </row>
-    <row r="233" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A233" s="3"/>
       <c r="B233" s="3" t="s">
         <v>39</v>
@@ -17958,7 +17940,7 @@
       <c r="AL233" s="3"/>
       <c r="AM233" s="3"/>
     </row>
-    <row r="234" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A234" s="3"/>
       <c r="B234" s="3" t="s">
         <v>39</v>
@@ -18027,7 +18009,7 @@
       <c r="AL234" s="3"/>
       <c r="AM234" s="3"/>
     </row>
-    <row r="235" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A235" s="3"/>
       <c r="B235" s="3" t="s">
         <v>39</v>
@@ -18096,7 +18078,7 @@
       <c r="AL235" s="3"/>
       <c r="AM235" s="3"/>
     </row>
-    <row r="236" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A236" s="3"/>
       <c r="B236" s="3" t="s">
         <v>39</v>
@@ -18167,7 +18149,7 @@
       <c r="AL236" s="3"/>
       <c r="AM236" s="3"/>
     </row>
-    <row r="237" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A237" s="3"/>
       <c r="B237" s="3" t="s">
         <v>39</v>
@@ -18238,7 +18220,7 @@
       <c r="AL237" s="3"/>
       <c r="AM237" s="3"/>
     </row>
-    <row r="238" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A238" s="3"/>
       <c r="B238" s="3" t="s">
         <v>39</v>
@@ -18309,7 +18291,7 @@
       <c r="AL238" s="3"/>
       <c r="AM238" s="3"/>
     </row>
-    <row r="239" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A239" s="3"/>
       <c r="B239" s="3" t="s">
         <v>39</v>
@@ -18380,7 +18362,7 @@
       <c r="AL239" s="3"/>
       <c r="AM239" s="3"/>
     </row>
-    <row r="240" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A240" s="3"/>
       <c r="B240" s="3" t="s">
         <v>39</v>
@@ -18451,7 +18433,7 @@
       <c r="AL240" s="3"/>
       <c r="AM240" s="3"/>
     </row>
-    <row r="241" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A241" s="3"/>
       <c r="B241" s="3" t="s">
         <v>39</v>
@@ -18522,7 +18504,7 @@
       <c r="AL241" s="3"/>
       <c r="AM241" s="3"/>
     </row>
-    <row r="242" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A242" s="3"/>
       <c r="B242" s="3" t="s">
         <v>39</v>
@@ -18593,7 +18575,7 @@
       <c r="AL242" s="3"/>
       <c r="AM242" s="3"/>
     </row>
-    <row r="243" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A243" s="3"/>
       <c r="B243" s="3" t="s">
         <v>39</v>
@@ -18664,7 +18646,7 @@
       <c r="AL243" s="3"/>
       <c r="AM243" s="3"/>
     </row>
-    <row r="244" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A244" s="3"/>
       <c r="B244" s="3" t="s">
         <v>39</v>
@@ -18733,7 +18715,7 @@
       <c r="AL244" s="3"/>
       <c r="AM244" s="3"/>
     </row>
-    <row r="245" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A245" s="3"/>
       <c r="B245" s="3" t="s">
         <v>39</v>
@@ -18802,7 +18784,7 @@
       <c r="AL245" s="3"/>
       <c r="AM245" s="3"/>
     </row>
-    <row r="246" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A246" s="3"/>
       <c r="B246" s="3" t="s">
         <v>39</v>
@@ -18869,7 +18851,7 @@
       <c r="AL246" s="3"/>
       <c r="AM246" s="3"/>
     </row>
-    <row r="247" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A247" s="3"/>
       <c r="B247" s="3" t="s">
         <v>39</v>
@@ -18936,7 +18918,7 @@
       <c r="AL247" s="3"/>
       <c r="AM247" s="3"/>
     </row>
-    <row r="248" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A248" s="3"/>
       <c r="B248" s="3" t="s">
         <v>39</v>
@@ -19003,7 +18985,7 @@
       <c r="AL248" s="3"/>
       <c r="AM248" s="3"/>
     </row>
-    <row r="249" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A249" s="3"/>
       <c r="B249" s="3" t="s">
         <v>39</v>
@@ -19070,7 +19052,7 @@
       <c r="AL249" s="3"/>
       <c r="AM249" s="3"/>
     </row>
-    <row r="250" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A250" s="3"/>
       <c r="B250" s="3" t="s">
         <v>39</v>
@@ -19137,7 +19119,7 @@
       <c r="AL250" s="3"/>
       <c r="AM250" s="3"/>
     </row>
-    <row r="251" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A251" s="3"/>
       <c r="B251" s="3" t="s">
         <v>39</v>
@@ -19204,7 +19186,7 @@
       <c r="AL251" s="3"/>
       <c r="AM251" s="3"/>
     </row>
-    <row r="252" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A252" s="3"/>
       <c r="B252" s="3" t="s">
         <v>39</v>
@@ -19273,7 +19255,7 @@
       <c r="AL252" s="3"/>
       <c r="AM252" s="3"/>
     </row>
-    <row r="253" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A253" s="3"/>
       <c r="B253" s="3" t="s">
         <v>39</v>
@@ -19342,7 +19324,7 @@
       <c r="AL253" s="3"/>
       <c r="AM253" s="3"/>
     </row>
-    <row r="254" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A254" s="3"/>
       <c r="B254" s="3" t="s">
         <v>39</v>
@@ -19411,7 +19393,7 @@
       <c r="AL254" s="3"/>
       <c r="AM254" s="3"/>
     </row>
-    <row r="255" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A255" s="3"/>
       <c r="B255" s="3" t="s">
         <v>39</v>
@@ -19480,7 +19462,7 @@
       <c r="AL255" s="3"/>
       <c r="AM255" s="3"/>
     </row>
-    <row r="256" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A256" s="3"/>
       <c r="B256" s="3" t="s">
         <v>39</v>
@@ -19547,7 +19529,7 @@
       <c r="AL256" s="3"/>
       <c r="AM256" s="3"/>
     </row>
-    <row r="257" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A257" s="3"/>
       <c r="B257" s="3" t="s">
         <v>39</v>
@@ -19614,7 +19596,7 @@
       <c r="AL257" s="3"/>
       <c r="AM257" s="3"/>
     </row>
-    <row r="258" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A258" s="3"/>
       <c r="B258" s="3" t="s">
         <v>39</v>
@@ -19683,7 +19665,7 @@
       <c r="AL258" s="3"/>
       <c r="AM258" s="3"/>
     </row>
-    <row r="259" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A259" s="3"/>
       <c r="B259" s="3" t="s">
         <v>39</v>
@@ -19752,7 +19734,7 @@
       <c r="AL259" s="3"/>
       <c r="AM259" s="3"/>
     </row>
-    <row r="260" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A260" s="3"/>
       <c r="B260" s="3" t="s">
         <v>39</v>
@@ -19821,7 +19803,7 @@
       <c r="AL260" s="3"/>
       <c r="AM260" s="3"/>
     </row>
-    <row r="261" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A261" s="3"/>
       <c r="B261" s="3" t="s">
         <v>39</v>
@@ -19890,7 +19872,7 @@
       <c r="AL261" s="3"/>
       <c r="AM261" s="3"/>
     </row>
-    <row r="262" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A262" s="3"/>
       <c r="B262" s="3" t="s">
         <v>39</v>
@@ -19959,7 +19941,7 @@
       <c r="AL262" s="3"/>
       <c r="AM262" s="3"/>
     </row>
-    <row r="263" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A263" s="3"/>
       <c r="B263" s="3" t="s">
         <v>39</v>
@@ -20028,7 +20010,7 @@
       <c r="AL263" s="3"/>
       <c r="AM263" s="3"/>
     </row>
-    <row r="264" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A264" s="3"/>
       <c r="B264" s="3" t="s">
         <v>39</v>
@@ -20097,7 +20079,7 @@
       <c r="AL264" s="3"/>
       <c r="AM264" s="3"/>
     </row>
-    <row r="265" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A265" s="3"/>
       <c r="B265" s="3" t="s">
         <v>39</v>
@@ -20166,7 +20148,7 @@
       <c r="AL265" s="3"/>
       <c r="AM265" s="3"/>
     </row>
-    <row r="266" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A266" s="3"/>
       <c r="B266" s="3" t="s">
         <v>39</v>
@@ -20235,7 +20217,7 @@
       <c r="AL266" s="3"/>
       <c r="AM266" s="3"/>
     </row>
-    <row r="267" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A267" s="3"/>
       <c r="B267" s="3" t="s">
         <v>39</v>
@@ -20304,7 +20286,7 @@
       <c r="AL267" s="3"/>
       <c r="AM267" s="3"/>
     </row>
-    <row r="268" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A268" s="3"/>
       <c r="B268" s="3" t="s">
         <v>39</v>
@@ -20373,7 +20355,7 @@
       <c r="AL268" s="3"/>
       <c r="AM268" s="3"/>
     </row>
-    <row r="269" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A269" s="3"/>
       <c r="B269" s="3" t="s">
         <v>39</v>
@@ -20442,7 +20424,7 @@
       <c r="AL269" s="3"/>
       <c r="AM269" s="3"/>
     </row>
-    <row r="270" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A270" s="3"/>
       <c r="B270" s="3" t="s">
         <v>39</v>
@@ -20511,7 +20493,7 @@
       <c r="AL270" s="3"/>
       <c r="AM270" s="3"/>
     </row>
-    <row r="271" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A271" s="3"/>
       <c r="B271" s="3" t="s">
         <v>39</v>
@@ -20578,7 +20560,7 @@
       <c r="AL271" s="3"/>
       <c r="AM271" s="3"/>
     </row>
-    <row r="272" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A272" s="3"/>
       <c r="B272" s="3" t="s">
         <v>39</v>
@@ -20645,7 +20627,7 @@
       <c r="AL272" s="3"/>
       <c r="AM272" s="3"/>
     </row>
-    <row r="273" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A273" s="3"/>
       <c r="B273" s="3" t="s">
         <v>39</v>
@@ -20712,7 +20694,7 @@
       <c r="AL273" s="3"/>
       <c r="AM273" s="3"/>
     </row>
-    <row r="274" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A274" s="3"/>
       <c r="B274" s="3" t="s">
         <v>39</v>
@@ -20779,7 +20761,7 @@
       <c r="AL274" s="3"/>
       <c r="AM274" s="3"/>
     </row>
-    <row r="275" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A275" s="3"/>
       <c r="B275" s="3" t="s">
         <v>39</v>
@@ -20848,7 +20830,7 @@
       <c r="AL275" s="3"/>
       <c r="AM275" s="3"/>
     </row>
-    <row r="276" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A276" s="3"/>
       <c r="B276" s="3" t="s">
         <v>39</v>
@@ -20917,7 +20899,7 @@
       <c r="AL276" s="3"/>
       <c r="AM276" s="3"/>
     </row>
-    <row r="277" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A277" s="3"/>
       <c r="B277" s="3" t="s">
         <v>39</v>
@@ -20986,7 +20968,7 @@
       <c r="AL277" s="3"/>
       <c r="AM277" s="3"/>
     </row>
-    <row r="278" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A278" s="3"/>
       <c r="B278" s="3" t="s">
         <v>39</v>
@@ -21055,7 +21037,7 @@
       <c r="AL278" s="3"/>
       <c r="AM278" s="3"/>
     </row>
-    <row r="279" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A279" s="3"/>
       <c r="B279" s="3" t="s">
         <v>39</v>
@@ -21124,7 +21106,7 @@
       <c r="AL279" s="3"/>
       <c r="AM279" s="3"/>
     </row>
-    <row r="280" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A280" s="3"/>
       <c r="B280" s="3" t="s">
         <v>39</v>
@@ -21193,7 +21175,7 @@
       <c r="AL280" s="3"/>
       <c r="AM280" s="3"/>
     </row>
-    <row r="281" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A281" s="3"/>
       <c r="B281" s="3" t="s">
         <v>39</v>
@@ -21262,7 +21244,7 @@
       <c r="AL281" s="3"/>
       <c r="AM281" s="3"/>
     </row>
-    <row r="282" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A282" s="3"/>
       <c r="B282" s="3" t="s">
         <v>39</v>
@@ -21331,7 +21313,7 @@
       <c r="AL282" s="3"/>
       <c r="AM282" s="3"/>
     </row>
-    <row r="283" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A283" s="3"/>
       <c r="B283" s="3" t="s">
         <v>39</v>
@@ -21400,7 +21382,7 @@
       <c r="AL283" s="3"/>
       <c r="AM283" s="3"/>
     </row>
-    <row r="284" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A284" s="3"/>
       <c r="B284" s="3" t="s">
         <v>39</v>
@@ -21469,7 +21451,7 @@
       <c r="AL284" s="3"/>
       <c r="AM284" s="3"/>
     </row>
-    <row r="285" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A285" s="3"/>
       <c r="B285" s="3" t="s">
         <v>39</v>
@@ -21538,7 +21520,7 @@
       <c r="AL285" s="3"/>
       <c r="AM285" s="3"/>
     </row>
-    <row r="286" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A286" s="3"/>
       <c r="B286" s="3" t="s">
         <v>39</v>
@@ -21605,7 +21587,7 @@
       <c r="AL286" s="3"/>
       <c r="AM286" s="3"/>
     </row>
-    <row r="287" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A287" s="3"/>
       <c r="B287" s="3" t="s">
         <v>39</v>
@@ -21672,7 +21654,7 @@
       <c r="AL287" s="3"/>
       <c r="AM287" s="3"/>
     </row>
-    <row r="288" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A288" s="3"/>
       <c r="B288" s="3" t="s">
         <v>39</v>
@@ -21739,7 +21721,7 @@
       <c r="AL288" s="3"/>
       <c r="AM288" s="3"/>
     </row>
-    <row r="289" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A289" s="3"/>
       <c r="B289" s="3" t="s">
         <v>39</v>
@@ -21806,7 +21788,7 @@
       <c r="AL289" s="3"/>
       <c r="AM289" s="3"/>
     </row>
-    <row r="290" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A290" s="3"/>
       <c r="B290" s="3" t="s">
         <v>39</v>
@@ -21873,7 +21855,7 @@
       <c r="AL290" s="3"/>
       <c r="AM290" s="3"/>
     </row>
-    <row r="291" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A291" s="3"/>
       <c r="B291" s="3" t="s">
         <v>39</v>
@@ -21940,7 +21922,7 @@
       <c r="AL291" s="3"/>
       <c r="AM291" s="3"/>
     </row>
-    <row r="292" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A292" s="3"/>
       <c r="B292" s="3" t="s">
         <v>39</v>
@@ -22009,7 +21991,7 @@
       <c r="AL292" s="3"/>
       <c r="AM292" s="3"/>
     </row>
-    <row r="293" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A293" s="3"/>
       <c r="B293" s="3" t="s">
         <v>39</v>
@@ -22078,7 +22060,7 @@
       <c r="AL293" s="3"/>
       <c r="AM293" s="3"/>
     </row>
-    <row r="294" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A294" s="3"/>
       <c r="B294" s="3" t="s">
         <v>39</v>
@@ -22147,7 +22129,7 @@
       <c r="AL294" s="3"/>
       <c r="AM294" s="3"/>
     </row>
-    <row r="295" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A295" s="3"/>
       <c r="B295" s="3" t="s">
         <v>39</v>
@@ -22216,7 +22198,7 @@
       <c r="AL295" s="3"/>
       <c r="AM295" s="3"/>
     </row>
-    <row r="296" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A296" s="3"/>
       <c r="B296" s="3" t="s">
         <v>39</v>
@@ -22283,7 +22265,7 @@
       <c r="AL296" s="3"/>
       <c r="AM296" s="3"/>
     </row>
-    <row r="297" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A297" s="3"/>
       <c r="B297" s="3" t="s">
         <v>39</v>
@@ -22350,7 +22332,7 @@
       <c r="AL297" s="3"/>
       <c r="AM297" s="3"/>
     </row>
-    <row r="298" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A298" s="3"/>
       <c r="B298" s="3" t="s">
         <v>39</v>
@@ -22419,7 +22401,7 @@
       <c r="AL298" s="3"/>
       <c r="AM298" s="3"/>
     </row>
-    <row r="299" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A299" s="3"/>
       <c r="B299" s="3" t="s">
         <v>39</v>
@@ -22488,7 +22470,7 @@
       <c r="AL299" s="3"/>
       <c r="AM299" s="3"/>
     </row>
-    <row r="300" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A300" s="3"/>
       <c r="B300" s="3" t="s">
         <v>39</v>
@@ -22557,7 +22539,7 @@
       <c r="AL300" s="3"/>
       <c r="AM300" s="3"/>
     </row>
-    <row r="301" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A301" s="3"/>
       <c r="B301" s="3" t="s">
         <v>39</v>
@@ -22626,7 +22608,7 @@
       <c r="AL301" s="3"/>
       <c r="AM301" s="3"/>
     </row>
-    <row r="302" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A302" s="3"/>
       <c r="B302" s="3" t="s">
         <v>39</v>
@@ -22695,7 +22677,7 @@
       <c r="AL302" s="3"/>
       <c r="AM302" s="3"/>
     </row>
-    <row r="303" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A303" s="3"/>
       <c r="B303" s="3" t="s">
         <v>39</v>
@@ -22764,7 +22746,7 @@
       <c r="AL303" s="3"/>
       <c r="AM303" s="3"/>
     </row>
-    <row r="304" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A304" s="3"/>
       <c r="B304" s="3" t="s">
         <v>39</v>
@@ -22833,7 +22815,7 @@
       <c r="AL304" s="3"/>
       <c r="AM304" s="3"/>
     </row>
-    <row r="305" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A305" s="3"/>
       <c r="B305" s="3" t="s">
         <v>39</v>
@@ -22902,7 +22884,7 @@
       <c r="AL305" s="3"/>
       <c r="AM305" s="3"/>
     </row>
-    <row r="306" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A306" s="3"/>
       <c r="B306" s="3" t="s">
         <v>39</v>
@@ -22971,7 +22953,7 @@
       <c r="AL306" s="3"/>
       <c r="AM306" s="3"/>
     </row>
-    <row r="307" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A307" s="3"/>
       <c r="B307" s="3" t="s">
         <v>39</v>
@@ -23040,7 +23022,7 @@
       <c r="AL307" s="3"/>
       <c r="AM307" s="3"/>
     </row>
-    <row r="308" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A308" s="3"/>
       <c r="B308" s="3" t="s">
         <v>39</v>
@@ -23109,7 +23091,7 @@
       <c r="AL308" s="3"/>
       <c r="AM308" s="3"/>
     </row>
-    <row r="309" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A309" s="3"/>
       <c r="B309" s="3" t="s">
         <v>39</v>
@@ -23178,7 +23160,7 @@
       <c r="AL309" s="3"/>
       <c r="AM309" s="3"/>
     </row>
-    <row r="310" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A310" s="3"/>
       <c r="B310" s="3" t="s">
         <v>39</v>
@@ -23247,7 +23229,7 @@
       <c r="AL310" s="3"/>
       <c r="AM310" s="3"/>
     </row>
-    <row r="311" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A311" s="3"/>
       <c r="B311" s="3" t="s">
         <v>39</v>
@@ -23314,7 +23296,7 @@
       <c r="AL311" s="3"/>
       <c r="AM311" s="3"/>
     </row>
-    <row r="312" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A312" s="3"/>
       <c r="B312" s="3" t="s">
         <v>39</v>
@@ -23381,7 +23363,7 @@
       <c r="AL312" s="3"/>
       <c r="AM312" s="3"/>
     </row>
-    <row r="313" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A313" s="3"/>
       <c r="B313" s="3" t="s">
         <v>39</v>
@@ -23448,7 +23430,7 @@
       <c r="AL313" s="3"/>
       <c r="AM313" s="3"/>
     </row>
-    <row r="314" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A314" s="3"/>
       <c r="B314" s="3" t="s">
         <v>39</v>
@@ -23515,7 +23497,7 @@
       <c r="AL314" s="3"/>
       <c r="AM314" s="3"/>
     </row>
-    <row r="315" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A315" s="3"/>
       <c r="B315" s="3" t="s">
         <v>39</v>
@@ -23584,7 +23566,7 @@
       <c r="AL315" s="3"/>
       <c r="AM315" s="3"/>
     </row>
-    <row r="316" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A316" s="3"/>
       <c r="B316" s="3" t="s">
         <v>39</v>
@@ -23653,7 +23635,7 @@
       <c r="AL316" s="3"/>
       <c r="AM316" s="3"/>
     </row>
-    <row r="317" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A317" s="3"/>
       <c r="B317" s="3" t="s">
         <v>39</v>
@@ -23722,7 +23704,7 @@
       <c r="AL317" s="3"/>
       <c r="AM317" s="3"/>
     </row>
-    <row r="318" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A318" s="3"/>
       <c r="B318" s="3" t="s">
         <v>39</v>
@@ -23791,7 +23773,7 @@
       <c r="AL318" s="3"/>
       <c r="AM318" s="3"/>
     </row>
-    <row r="319" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A319" s="3"/>
       <c r="B319" s="3" t="s">
         <v>39</v>
@@ -23860,7 +23842,7 @@
       <c r="AL319" s="3"/>
       <c r="AM319" s="3"/>
     </row>
-    <row r="320" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A320" s="3"/>
       <c r="B320" s="3" t="s">
         <v>39</v>
@@ -23929,7 +23911,7 @@
       <c r="AL320" s="3"/>
       <c r="AM320" s="3"/>
     </row>
-    <row r="321" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A321" s="3"/>
       <c r="B321" s="3" t="s">
         <v>39</v>
@@ -23998,7 +23980,7 @@
       <c r="AL321" s="3"/>
       <c r="AM321" s="3"/>
     </row>
-    <row r="322" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A322" s="3"/>
       <c r="B322" s="3" t="s">
         <v>39</v>
@@ -24067,7 +24049,7 @@
       <c r="AL322" s="3"/>
       <c r="AM322" s="3"/>
     </row>
-    <row r="323" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A323" s="3"/>
       <c r="B323" s="3" t="s">
         <v>39</v>
@@ -24136,7 +24118,7 @@
       <c r="AL323" s="3"/>
       <c r="AM323" s="3"/>
     </row>
-    <row r="324" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A324" s="3"/>
       <c r="B324" s="3" t="s">
         <v>39</v>
@@ -24205,7 +24187,7 @@
       <c r="AL324" s="3"/>
       <c r="AM324" s="3"/>
     </row>
-    <row r="325" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A325" s="3"/>
       <c r="B325" s="3" t="s">
         <v>39</v>
